--- a/output/topology_excel/5581.xlsx
+++ b/output/topology_excel/5581.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F84"/>
+  <dimension ref="A1:F92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,10 +462,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -484,10 +484,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -506,10 +506,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -528,10 +528,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -550,10 +550,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B6" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -572,10 +572,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="B7" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -594,10 +594,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -616,10 +616,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B9" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -638,10 +638,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -660,10 +660,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B11" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -682,10 +682,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="B12" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -704,10 +704,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B13" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -726,10 +726,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B14" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -748,10 +748,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B15" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -770,10 +770,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B16" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -792,10 +792,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="B17" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -814,10 +814,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="B18" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -836,10 +836,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B19" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -858,10 +858,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="B20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="F20" t="n">
         <v>11</v>
@@ -880,10 +880,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -924,10 +924,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="B23" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F23" t="n">
         <v>11</v>
@@ -946,7 +946,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B24" t="n">
         <v>22</v>
@@ -960,7 +960,7 @@
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="F24" t="n">
         <v>11</v>
@@ -968,10 +968,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B25" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>116</v>
+        <v>66</v>
       </c>
       <c r="F25" t="n">
         <v>11</v>
@@ -990,10 +990,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B26" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>67</v>
+        <v>116</v>
       </c>
       <c r="F26" t="n">
         <v>11</v>
@@ -1012,10 +1012,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B27" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F27" t="n">
         <v>11</v>
@@ -1034,24 +1034,24 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Wall</t>
+          <t>Door</t>
         </is>
       </c>
       <c r="D28" t="n">
         <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>330</v>
+        <v>68</v>
       </c>
       <c r="F28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29">
@@ -1059,7 +1059,7 @@
         <v>1</v>
       </c>
       <c r="B29" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>349</v>
+        <v>326</v>
       </c>
       <c r="F29" t="n">
         <v>11</v>
@@ -1078,10 +1078,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B30" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>369</v>
+        <v>179</v>
       </c>
       <c r="F30" t="n">
         <v>11</v>
@@ -1100,10 +1100,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B31" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1114,10 +1114,10 @@
         <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>313</v>
+        <v>238</v>
       </c>
       <c r="F31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32">
@@ -1125,7 +1125,7 @@
         <v>2</v>
       </c>
       <c r="B32" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1136,10 +1136,10 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>373</v>
+        <v>186</v>
       </c>
       <c r="F32" t="n">
-        <v>11</v>
+        <v>63</v>
       </c>
     </row>
     <row r="33">
@@ -1147,7 +1147,7 @@
         <v>2</v>
       </c>
       <c r="B33" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1158,10 +1158,10 @@
         <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>189</v>
+        <v>152</v>
       </c>
       <c r="F33" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="34">
@@ -1169,7 +1169,7 @@
         <v>2</v>
       </c>
       <c r="B34" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>376</v>
+        <v>392</v>
       </c>
       <c r="F34" t="n">
         <v>11</v>
@@ -1188,10 +1188,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B35" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>105</v>
+        <v>330</v>
       </c>
       <c r="F35" t="n">
         <v>10</v>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B36" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1224,18 +1224,18 @@
         <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>158</v>
+        <v>349</v>
       </c>
       <c r="F36" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B37" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1246,18 +1246,18 @@
         <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>143</v>
+        <v>369</v>
       </c>
       <c r="F37" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B38" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1276,10 +1276,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B39" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1290,18 +1290,18 @@
         <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>186</v>
+        <v>313</v>
       </c>
       <c r="F39" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B40" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>152</v>
+        <v>186</v>
       </c>
       <c r="F40" t="n">
         <v>11</v>
@@ -1323,7 +1323,7 @@
         <v>5</v>
       </c>
       <c r="B41" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>295</v>
+        <v>152</v>
       </c>
       <c r="F41" t="n">
         <v>11</v>
@@ -1345,7 +1345,7 @@
         <v>6</v>
       </c>
       <c r="B42" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>189</v>
+        <v>373</v>
       </c>
       <c r="F42" t="n">
         <v>11</v>
@@ -1367,7 +1367,7 @@
         <v>6</v>
       </c>
       <c r="B43" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>45</v>
+        <v>295</v>
       </c>
       <c r="F43" t="n">
         <v>11</v>
@@ -1386,10 +1386,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B44" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>186</v>
+        <v>376</v>
       </c>
       <c r="F44" t="n">
         <v>11</v>
@@ -1411,7 +1411,7 @@
         <v>7</v>
       </c>
       <c r="B45" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1422,18 +1422,18 @@
         <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>152</v>
+        <v>17</v>
       </c>
       <c r="F45" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B46" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
         <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>17</v>
+        <v>268</v>
       </c>
       <c r="F46" t="n">
         <v>16</v>
@@ -1455,7 +1455,7 @@
         <v>8</v>
       </c>
       <c r="B47" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1466,19 +1466,19 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>268</v>
+        <v>90</v>
       </c>
       <c r="F47" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
+        <v>8</v>
+      </c>
+      <c r="B48" t="n">
         <v>9</v>
       </c>
-      <c r="B48" t="n">
-        <v>10</v>
-      </c>
       <c r="C48" t="inlineStr">
         <is>
           <t>Wall</t>
@@ -1488,18 +1488,18 @@
         <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>49</v>
+        <v>296</v>
       </c>
       <c r="F48" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B49" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -1510,18 +1510,18 @@
         <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="F49" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -1532,18 +1532,18 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>158</v>
+        <v>375</v>
       </c>
       <c r="F50" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -1554,18 +1554,18 @@
         <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>186</v>
+        <v>374</v>
       </c>
       <c r="F51" t="n">
-        <v>63</v>
+        <v>10</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B52" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -1576,18 +1576,18 @@
         <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>152</v>
+        <v>377</v>
       </c>
       <c r="F52" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B53" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -1598,18 +1598,18 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>434</v>
+        <v>201</v>
       </c>
       <c r="F53" t="n">
-        <v>165</v>
+        <v>10</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B54" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -1620,18 +1620,18 @@
         <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>102</v>
+        <v>298</v>
       </c>
       <c r="F54" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B55" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -1642,18 +1642,18 @@
         <v>1</v>
       </c>
       <c r="E55" t="n">
-        <v>143</v>
+        <v>86</v>
       </c>
       <c r="F55" t="n">
-        <v>53</v>
+        <v>10</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B56" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -1664,10 +1664,10 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>143</v>
+        <v>371</v>
       </c>
       <c r="F56" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="57">
@@ -1675,7 +1675,7 @@
         <v>12</v>
       </c>
       <c r="B57" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -1686,10 +1686,10 @@
         <v>1</v>
       </c>
       <c r="E57" t="n">
-        <v>135</v>
+        <v>189</v>
       </c>
       <c r="F57" t="n">
-        <v>60</v>
+        <v>11</v>
       </c>
     </row>
     <row r="58">
@@ -1697,7 +1697,7 @@
         <v>12</v>
       </c>
       <c r="B58" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>93</v>
+        <v>45</v>
       </c>
       <c r="F58" t="n">
         <v>11</v>
@@ -1719,7 +1719,7 @@
         <v>12</v>
       </c>
       <c r="B59" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>130</v>
+        <v>186</v>
       </c>
       <c r="F59" t="n">
         <v>11</v>
@@ -1738,10 +1738,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B60" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -1752,10 +1752,10 @@
         <v>1</v>
       </c>
       <c r="E60" t="n">
-        <v>249</v>
+        <v>152</v>
       </c>
       <c r="F60" t="n">
-        <v>223</v>
+        <v>11</v>
       </c>
     </row>
     <row r="61">
@@ -1763,7 +1763,7 @@
         <v>13</v>
       </c>
       <c r="B61" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>61</v>
+        <v>105</v>
       </c>
       <c r="F61" t="n">
         <v>10</v>
@@ -1785,7 +1785,7 @@
         <v>13</v>
       </c>
       <c r="B62" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -1796,19 +1796,19 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>182</v>
+        <v>49</v>
       </c>
       <c r="F62" t="n">
-        <v>113</v>
+        <v>11</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
+        <v>13</v>
+      </c>
+      <c r="B63" t="n">
         <v>14</v>
       </c>
-      <c r="B63" t="n">
-        <v>15</v>
-      </c>
       <c r="C63" t="inlineStr">
         <is>
           <t>Wall</t>
@@ -1818,10 +1818,10 @@
         <v>1</v>
       </c>
       <c r="E63" t="n">
-        <v>90</v>
+        <v>152</v>
       </c>
       <c r="F63" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="64">
@@ -1829,7 +1829,7 @@
         <v>14</v>
       </c>
       <c r="B64" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -1840,10 +1840,10 @@
         <v>1</v>
       </c>
       <c r="E64" t="n">
-        <v>18</v>
+        <v>158</v>
       </c>
       <c r="F64" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="65">
@@ -1851,7 +1851,7 @@
         <v>14</v>
       </c>
       <c r="B65" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>133</v>
+        <v>158</v>
       </c>
       <c r="F65" t="n">
         <v>10</v>
@@ -1873,7 +1873,7 @@
         <v>15</v>
       </c>
       <c r="B66" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -1884,10 +1884,10 @@
         <v>1</v>
       </c>
       <c r="E66" t="n">
-        <v>296</v>
+        <v>182</v>
       </c>
       <c r="F66" t="n">
-        <v>10</v>
+        <v>113</v>
       </c>
     </row>
     <row r="67">
@@ -1895,18 +1895,18 @@
         <v>15</v>
       </c>
       <c r="B67" t="n">
+        <v>27</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" t="n">
         <v>18</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>1</v>
-      </c>
-      <c r="E67" t="n">
-        <v>196</v>
       </c>
       <c r="F67" t="n">
         <v>10</v>
@@ -1917,7 +1917,7 @@
         <v>15</v>
       </c>
       <c r="B68" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>375</v>
+        <v>143</v>
       </c>
       <c r="F68" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B69" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
         <v>1</v>
       </c>
       <c r="E69" t="n">
-        <v>374</v>
+        <v>102</v>
       </c>
       <c r="F69" t="n">
         <v>10</v>
@@ -1958,10 +1958,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B70" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>1</v>
       </c>
       <c r="E70" t="n">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="F70" t="n">
         <v>10</v>
@@ -1980,10 +1980,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B71" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -1994,18 +1994,18 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>377</v>
+        <v>143</v>
       </c>
       <c r="F71" t="n">
-        <v>11</v>
+        <v>53</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B72" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -2016,18 +2016,18 @@
         <v>1</v>
       </c>
       <c r="E72" t="n">
-        <v>371</v>
+        <v>135</v>
       </c>
       <c r="F72" t="n">
-        <v>11</v>
+        <v>60</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B73" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -2046,10 +2046,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B74" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -2068,10 +2068,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B75" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -2090,11 +2090,11 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
+        <v>18</v>
+      </c>
+      <c r="B76" t="n">
         <v>21</v>
       </c>
-      <c r="B76" t="n">
-        <v>22</v>
-      </c>
       <c r="C76" t="inlineStr">
         <is>
           <t>Wall</t>
@@ -2104,7 +2104,7 @@
         <v>1</v>
       </c>
       <c r="E76" t="n">
-        <v>141</v>
+        <v>93</v>
       </c>
       <c r="F76" t="n">
         <v>11</v>
@@ -2112,10 +2112,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B77" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>93</v>
+        <v>141</v>
       </c>
       <c r="F77" t="n">
         <v>11</v>
@@ -2134,10 +2134,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B78" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -2148,18 +2148,18 @@
         <v>1</v>
       </c>
       <c r="E78" t="n">
-        <v>201</v>
+        <v>93</v>
       </c>
       <c r="F78" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B79" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         <v>1</v>
       </c>
       <c r="E79" t="n">
-        <v>49</v>
+        <v>130</v>
       </c>
       <c r="F79" t="n">
         <v>11</v>
@@ -2178,10 +2178,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B80" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>130</v>
+        <v>49</v>
       </c>
       <c r="F80" t="n">
         <v>11</v>
@@ -2200,10 +2200,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B81" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
         <v>1</v>
       </c>
       <c r="E81" t="n">
-        <v>298</v>
+        <v>130</v>
       </c>
       <c r="F81" t="n">
         <v>11</v>
@@ -2222,10 +2222,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B82" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>1</v>
       </c>
       <c r="E82" t="n">
-        <v>86</v>
+        <v>189</v>
       </c>
       <c r="F82" t="n">
         <v>10</v>
@@ -2244,10 +2244,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B83" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -2258,32 +2258,208 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F83" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
+        <v>21</v>
+      </c>
+      <c r="B84" t="n">
         <v>26</v>
       </c>
-      <c r="B84" t="n">
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>1</v>
+      </c>
+      <c r="E84" t="n">
+        <v>434</v>
+      </c>
+      <c r="F84" t="n">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>21</v>
+      </c>
+      <c r="B85" t="n">
+        <v>22</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" t="n">
+        <v>143</v>
+      </c>
+      <c r="F85" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>21</v>
+      </c>
+      <c r="B86" t="n">
+        <v>23</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>1</v>
+      </c>
+      <c r="E86" t="n">
+        <v>212</v>
+      </c>
+      <c r="F86" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>23</v>
+      </c>
+      <c r="B87" t="n">
+        <v>28</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>1</v>
+      </c>
+      <c r="E87" t="n">
+        <v>146</v>
+      </c>
+      <c r="F87" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>26</v>
+      </c>
+      <c r="B88" t="n">
         <v>27</v>
       </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>1</v>
-      </c>
-      <c r="E84" t="n">
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" t="n">
+        <v>61</v>
+      </c>
+      <c r="F88" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>28</v>
+      </c>
+      <c r="B89" t="n">
+        <v>29</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>1</v>
+      </c>
+      <c r="E89" t="n">
         <v>86</v>
       </c>
-      <c r="F84" t="n">
-        <v>11</v>
+      <c r="F89" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>2</v>
+      </c>
+      <c r="B90" t="n">
+        <v>21</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>1</v>
+      </c>
+      <c r="E90" t="n">
+        <v>108</v>
+      </c>
+      <c r="F90" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>2</v>
+      </c>
+      <c r="B91" t="n">
+        <v>21</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>1</v>
+      </c>
+      <c r="E91" t="n">
+        <v>117</v>
+      </c>
+      <c r="F91" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>1</v>
+      </c>
+      <c r="B92" t="n">
+        <v>2</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>1</v>
+      </c>
+      <c r="E92" t="n">
+        <v>159</v>
+      </c>
+      <c r="F92" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/topology_excel/5581.xlsx
+++ b/output/topology_excel/5581.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F92"/>
+  <dimension ref="A1:H91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,22 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>Length_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Width_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Length_2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Width_2</t>
         </is>
       </c>
     </row>
@@ -481,6 +491,8 @@
       <c r="F2" t="n">
         <v>10</v>
       </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -503,6 +515,8 @@
       <c r="F3" t="n">
         <v>11</v>
       </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -525,6 +539,8 @@
       <c r="F4" t="n">
         <v>10</v>
       </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -547,6 +563,8 @@
       <c r="F5" t="n">
         <v>11</v>
       </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -569,6 +587,8 @@
       <c r="F6" t="n">
         <v>11</v>
       </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -591,6 +611,8 @@
       <c r="F7" t="n">
         <v>10</v>
       </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -613,6 +635,8 @@
       <c r="F8" t="n">
         <v>11</v>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -635,6 +659,8 @@
       <c r="F9" t="n">
         <v>11</v>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -657,6 +683,8 @@
       <c r="F10" t="n">
         <v>11</v>
       </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -679,6 +707,8 @@
       <c r="F11" t="n">
         <v>10</v>
       </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -701,6 +731,8 @@
       <c r="F12" t="n">
         <v>16</v>
       </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -723,6 +755,8 @@
       <c r="F13" t="n">
         <v>10</v>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -745,6 +779,8 @@
       <c r="F14" t="n">
         <v>10</v>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -767,6 +803,8 @@
       <c r="F15" t="n">
         <v>10</v>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -789,6 +827,8 @@
       <c r="F16" t="n">
         <v>10</v>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -811,6 +851,8 @@
       <c r="F17" t="n">
         <v>10</v>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -833,6 +875,8 @@
       <c r="F18" t="n">
         <v>10</v>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -855,6 +899,8 @@
       <c r="F19" t="n">
         <v>10</v>
       </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -877,6 +923,8 @@
       <c r="F20" t="n">
         <v>11</v>
       </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -899,6 +947,8 @@
       <c r="F21" t="n">
         <v>11</v>
       </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -921,6 +971,8 @@
       <c r="F22" t="n">
         <v>11</v>
       </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -943,6 +995,8 @@
       <c r="F23" t="n">
         <v>11</v>
       </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -965,6 +1019,8 @@
       <c r="F24" t="n">
         <v>11</v>
       </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -987,6 +1043,8 @@
       <c r="F25" t="n">
         <v>11</v>
       </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1009,6 +1067,8 @@
       <c r="F26" t="n">
         <v>11</v>
       </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1031,6 +1091,8 @@
       <c r="F27" t="n">
         <v>11</v>
       </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1053,6 +1115,8 @@
       <c r="F28" t="n">
         <v>11</v>
       </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1075,6 +1139,8 @@
       <c r="F29" t="n">
         <v>11</v>
       </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1097,6 +1163,8 @@
       <c r="F30" t="n">
         <v>11</v>
       </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1119,6 +1187,8 @@
       <c r="F31" t="n">
         <v>11</v>
       </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1139,8 +1209,10 @@
         <v>186</v>
       </c>
       <c r="F32" t="n">
-        <v>63</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1163,6 +1235,8 @@
       <c r="F33" t="n">
         <v>16</v>
       </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1177,12 +1251,18 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E34" t="n">
-        <v>392</v>
+        <v>222</v>
       </c>
       <c r="F34" t="n">
+        <v>11</v>
+      </c>
+      <c r="G34" t="n">
+        <v>53</v>
+      </c>
+      <c r="H34" t="n">
         <v>11</v>
       </c>
     </row>
@@ -1207,6 +1287,8 @@
       <c r="F35" t="n">
         <v>10</v>
       </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1229,6 +1311,8 @@
       <c r="F36" t="n">
         <v>11</v>
       </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1251,6 +1335,8 @@
       <c r="F37" t="n">
         <v>11</v>
       </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1273,6 +1359,8 @@
       <c r="F38" t="n">
         <v>11</v>
       </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1295,6 +1383,8 @@
       <c r="F39" t="n">
         <v>10</v>
       </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1317,6 +1407,8 @@
       <c r="F40" t="n">
         <v>11</v>
       </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1339,6 +1431,8 @@
       <c r="F41" t="n">
         <v>11</v>
       </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1361,6 +1455,8 @@
       <c r="F42" t="n">
         <v>11</v>
       </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1383,6 +1479,8 @@
       <c r="F43" t="n">
         <v>11</v>
       </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1405,6 +1503,8 @@
       <c r="F44" t="n">
         <v>11</v>
       </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1427,6 +1527,8 @@
       <c r="F45" t="n">
         <v>16</v>
       </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1449,6 +1551,8 @@
       <c r="F46" t="n">
         <v>16</v>
       </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1471,6 +1575,8 @@
       <c r="F47" t="n">
         <v>10</v>
       </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1493,6 +1599,8 @@
       <c r="F48" t="n">
         <v>10</v>
       </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1515,6 +1623,8 @@
       <c r="F49" t="n">
         <v>10</v>
       </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1537,6 +1647,8 @@
       <c r="F50" t="n">
         <v>10</v>
       </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1559,6 +1671,8 @@
       <c r="F51" t="n">
         <v>10</v>
       </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1581,6 +1695,8 @@
       <c r="F52" t="n">
         <v>11</v>
       </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1603,6 +1719,8 @@
       <c r="F53" t="n">
         <v>10</v>
       </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1625,6 +1743,8 @@
       <c r="F54" t="n">
         <v>11</v>
       </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1647,6 +1767,8 @@
       <c r="F55" t="n">
         <v>10</v>
       </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1669,6 +1791,8 @@
       <c r="F56" t="n">
         <v>11</v>
       </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -1691,6 +1815,8 @@
       <c r="F57" t="n">
         <v>11</v>
       </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -1713,6 +1839,8 @@
       <c r="F58" t="n">
         <v>11</v>
       </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -1735,6 +1863,8 @@
       <c r="F59" t="n">
         <v>11</v>
       </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -1757,6 +1887,8 @@
       <c r="F60" t="n">
         <v>11</v>
       </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -1779,6 +1911,8 @@
       <c r="F61" t="n">
         <v>10</v>
       </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -1801,6 +1935,8 @@
       <c r="F62" t="n">
         <v>11</v>
       </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -1823,6 +1959,8 @@
       <c r="F63" t="n">
         <v>12</v>
       </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -1845,6 +1983,8 @@
       <c r="F64" t="n">
         <v>11</v>
       </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -1867,6 +2007,8 @@
       <c r="F65" t="n">
         <v>10</v>
       </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -1881,13 +2023,19 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>182</v>
+        <v>102</v>
       </c>
       <c r="F66" t="n">
-        <v>113</v>
+        <v>11</v>
+      </c>
+      <c r="G66" t="n">
+        <v>171</v>
+      </c>
+      <c r="H66" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="67">
@@ -1911,6 +2059,8 @@
       <c r="F67" t="n">
         <v>10</v>
       </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -1933,6 +2083,8 @@
       <c r="F68" t="n">
         <v>10</v>
       </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -1955,6 +2107,8 @@
       <c r="F69" t="n">
         <v>10</v>
       </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -1977,6 +2131,8 @@
       <c r="F70" t="n">
         <v>10</v>
       </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -1991,13 +2147,19 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E71" t="n">
-        <v>143</v>
+        <v>43</v>
       </c>
       <c r="F71" t="n">
-        <v>53</v>
+        <v>10</v>
+      </c>
+      <c r="G71" t="n">
+        <v>133</v>
+      </c>
+      <c r="H71" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="72">
@@ -2013,13 +2175,19 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="F72" t="n">
-        <v>60</v>
+        <v>11</v>
+      </c>
+      <c r="G72" t="n">
+        <v>49</v>
+      </c>
+      <c r="H72" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="73">
@@ -2043,6 +2211,8 @@
       <c r="F73" t="n">
         <v>11</v>
       </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -2065,6 +2235,8 @@
       <c r="F74" t="n">
         <v>11</v>
       </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -2087,6 +2259,8 @@
       <c r="F75" t="n">
         <v>11</v>
       </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -2109,6 +2283,8 @@
       <c r="F76" t="n">
         <v>11</v>
       </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -2131,6 +2307,8 @@
       <c r="F77" t="n">
         <v>11</v>
       </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -2153,6 +2331,8 @@
       <c r="F78" t="n">
         <v>11</v>
       </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -2175,6 +2355,8 @@
       <c r="F79" t="n">
         <v>11</v>
       </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -2197,6 +2379,8 @@
       <c r="F80" t="n">
         <v>11</v>
       </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -2219,6 +2403,8 @@
       <c r="F81" t="n">
         <v>11</v>
       </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -2241,6 +2427,8 @@
       <c r="F82" t="n">
         <v>10</v>
       </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -2263,6 +2451,8 @@
       <c r="F83" t="n">
         <v>16</v>
       </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -2277,13 +2467,19 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>434</v>
+        <v>424</v>
       </c>
       <c r="F84" t="n">
-        <v>165</v>
+        <v>10</v>
+      </c>
+      <c r="G84" t="n">
+        <v>155</v>
+      </c>
+      <c r="H84" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="85">
@@ -2307,6 +2503,8 @@
       <c r="F85" t="n">
         <v>10</v>
       </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -2329,6 +2527,8 @@
       <c r="F86" t="n">
         <v>11</v>
       </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -2351,6 +2551,8 @@
       <c r="F87" t="n">
         <v>11</v>
       </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -2373,6 +2575,8 @@
       <c r="F88" t="n">
         <v>10</v>
       </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -2395,6 +2599,8 @@
       <c r="F89" t="n">
         <v>11</v>
       </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -2409,7 +2615,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E90" t="n">
         <v>108</v>
@@ -2417,14 +2623,20 @@
       <c r="F90" t="n">
         <v>1</v>
       </c>
+      <c r="G90" t="n">
+        <v>117</v>
+      </c>
+      <c r="H90" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
+        <v>1</v>
+      </c>
+      <c r="B91" t="n">
         <v>2</v>
       </c>
-      <c r="B91" t="n">
-        <v>21</v>
-      </c>
       <c r="C91" t="inlineStr">
         <is>
           <t>Opening</t>
@@ -2434,33 +2646,13 @@
         <v>1</v>
       </c>
       <c r="E91" t="n">
-        <v>117</v>
+        <v>159</v>
       </c>
       <c r="F91" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="n">
-        <v>1</v>
-      </c>
-      <c r="B92" t="n">
-        <v>2</v>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Opening</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>1</v>
-      </c>
-      <c r="E92" t="n">
-        <v>159</v>
-      </c>
-      <c r="F92" t="n">
-        <v>1</v>
-      </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
